--- a/Corte_1.xlsx
+++ b/Corte_1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30431"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Descargas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2417" documentId="13_ncr:1_{623D021F-1D2B-4193-BE32-C6604CE1B927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B7A680C-4751-4911-8F2A-461E5A8B857B}"/>
+  <xr:revisionPtr revIDLastSave="2518" documentId="13_ncr:1_{623D021F-1D2B-4193-BE32-C6604CE1B927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C319B7C2-4EAD-4F0E-B021-5143196226EB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="90">
   <si>
     <t>Asignatura</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>Taller 2</t>
+  </si>
+  <si>
+    <t>Kahoot</t>
   </si>
 </sst>
 </file>
@@ -516,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -560,51 +563,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -619,9 +577,6 @@
     <xf numFmtId="9" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -634,6 +589,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1177,49 +1191,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="18" t="s">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
     </row>
     <row r="2" spans="1:23">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
     </row>
     <row r="3" spans="1:23">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="25" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="30"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="45"/>
       <c r="N3" s="12"/>
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
@@ -1228,40 +1242,40 @@
       <c r="S3" s="12"/>
     </row>
     <row r="4" spans="1:23">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="28"/>
+      <c r="C4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
     </row>
     <row r="6" spans="1:23">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="4">
         <v>0.2</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="31"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="44"/>
       <c r="L6" s="3">
         <v>0.3</v>
       </c>
@@ -1271,13 +1285,13 @@
       <c r="N6" s="4">
         <v>0.5</v>
       </c>
-      <c r="O6" s="27" t="s">
+      <c r="O6" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="29"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="40"/>
       <c r="T6" s="11" t="s">
         <v>13</v>
       </c>
@@ -1292,14 +1306,14 @@
       </c>
     </row>
     <row r="7" spans="1:23">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22" t="s">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="22"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="8" t="s">
         <v>19</v>
       </c>
@@ -2593,14 +2607,14 @@
       </c>
     </row>
     <row r="33" spans="1:23">
-      <c r="A33" s="35">
+      <c r="A33" s="20">
         <v>1011098258</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35" t="s">
+      <c r="B33" s="20"/>
+      <c r="C33" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="36"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="5"/>
       <c r="F33" s="1">
         <f>E33*0.1</f>
@@ -2843,15 +2857,15 @@
       </c>
     </row>
     <row r="38" spans="1:23">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B38" s="33"/>
-      <c r="C38" s="32" t="s">
+      <c r="B38" s="18"/>
+      <c r="C38" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D38" s="42"/>
-      <c r="E38" s="34"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="19"/>
       <c r="F38" s="1">
         <f>E38*0.1</f>
         <v>0</v>
@@ -2893,14 +2907,14 @@
       </c>
     </row>
     <row r="39" spans="1:23">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="14" t="s">
+      <c r="B39" s="47"/>
+      <c r="C39" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="16"/>
+      <c r="D39" s="27"/>
       <c r="E39" s="1"/>
       <c r="F39" s="5">
         <f>E39*0.1</f>
@@ -2951,11 +2965,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="15">
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
@@ -2964,6 +2973,11 @@
     <mergeCell ref="C4:I4"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="G6:K6"/>
     <mergeCell ref="A6:D6"/>
   </mergeCells>
@@ -3028,84 +3042,84 @@
     <col min="5" max="5" width="18.140625" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="10" max="10" width="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" customWidth="1"/>
     <col min="14" max="14" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="18" t="s">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="25" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="28"/>
+      <c r="C4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19" t="s">
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="37">
+      <c r="F6" s="34"/>
+      <c r="G6" s="22">
         <v>0.5</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="37">
+      <c r="I6" s="22">
         <v>0.5</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="K6" s="37" t="s">
+      <c r="K6" s="22" t="s">
         <v>13</v>
       </c>
       <c r="L6" s="2" t="s">
@@ -3119,30 +3133,32 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38" t="s">
+      <c r="B7" s="35"/>
+      <c r="C7" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="39" t="s">
+      <c r="D7" s="35"/>
+      <c r="E7" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="F7" s="39" t="s">
+      <c r="F7" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="G7" s="40"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="39"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="23"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="14" t="s">
@@ -3170,18 +3186,20 @@
         <f>H8*0.5</f>
         <v>1.5</v>
       </c>
-      <c r="J8" s="6"/>
+      <c r="J8" s="6">
+        <v>2</v>
+      </c>
       <c r="K8" s="6">
-        <f>(SUM(J8:J8)/5)*0.3</f>
-        <v>0</v>
+        <f>(SUM(J8:J8)/5)*0.5</f>
+        <v>0.2</v>
       </c>
       <c r="L8" s="6">
         <f>I8+G8</f>
         <v>3.8</v>
       </c>
       <c r="M8" s="6">
-        <f>INT(L8*10)/10+IF(MOD(L8*10,1)&gt;=0.5,0.1,0)</f>
-        <v>3.8</v>
+        <f>INT(L8*10)/10+IF(MOD(L8*10,1)&gt;=0.5,0.1,0)+K8</f>
+        <v>4</v>
       </c>
       <c r="N8" s="1" t="str">
         <f>IF(L8&lt;3,3-L8,"No aplica")</f>
@@ -3214,18 +3232,20 @@
         <f>H9*0.5</f>
         <v>1.8</v>
       </c>
-      <c r="J9" s="6"/>
+      <c r="J9" s="6">
+        <v>1</v>
+      </c>
       <c r="K9" s="6">
         <f>(SUM(J9:J9)/5)*0.5</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L9" s="6">
         <f>I9+G9</f>
         <v>4.1749999999999998</v>
       </c>
       <c r="M9" s="6">
-        <f>INT(L9*10)/10+IF(MOD(L9*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.1999999999999993</v>
+        <f t="shared" ref="M9:M39" si="0">INT(L9*10)/10+IF(MOD(L9*10,1)&gt;=0.5,0.1,0)+K9</f>
+        <v>4.2999999999999989</v>
       </c>
       <c r="N9" s="1" t="str">
         <f>IF(L9&lt;3,3-L9,"No aplica")</f>
@@ -3258,18 +3278,20 @@
         <f>H10*0.5</f>
         <v>2.15</v>
       </c>
-      <c r="J10" s="6"/>
+      <c r="J10" s="6">
+        <v>2</v>
+      </c>
       <c r="K10" s="6">
         <f>(SUM(J10:J10)/5)*0.5</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L10" s="6">
         <f>I10+G10</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="M10" s="6">
-        <f>INT(L10*10)/10+IF(MOD(L10*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>4.8</v>
       </c>
       <c r="N10" s="1" t="str">
         <f>IF(L10&lt;3,3-L10,"No aplica")</f>
@@ -3302,18 +3324,20 @@
         <f>H11*0.5</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="J11" s="6"/>
+      <c r="J11" s="6">
+        <v>1</v>
+      </c>
       <c r="K11" s="6">
         <f>(SUM(J11:J11)/5)*0.5</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L11" s="6">
         <f>I11+G11</f>
         <v>4.4250000000000007</v>
       </c>
       <c r="M11" s="6">
-        <f>INT(L11*10)/10+IF(MOD(L11*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.4000000000000004</v>
+        <f>INT(L11*10)/10+IF(MOD(L11*10,1)&gt;=0.5,0.1,0)+K11</f>
+        <v>4.5</v>
       </c>
       <c r="N11" s="1" t="str">
         <f>IF(L11&lt;3,3-L11,"No aplica")</f>
@@ -3346,18 +3370,20 @@
         <f>H12*0.5</f>
         <v>2.35</v>
       </c>
-      <c r="J12" s="6"/>
+      <c r="J12" s="6">
+        <v>2</v>
+      </c>
       <c r="K12" s="6">
         <f>(SUM(J12:J12)/5)*0.5</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L12" s="6">
         <f>I12+G12</f>
         <v>4.7750000000000004</v>
       </c>
       <c r="M12" s="6">
-        <f>INT(L12*10)/10+IF(MOD(L12*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="N12" s="1" t="str">
         <f>IF(L12&lt;3,3-L12,"No aplica")</f>
@@ -3390,18 +3416,20 @@
         <f>H13*0.5</f>
         <v>1.85</v>
       </c>
-      <c r="J13" s="6"/>
+      <c r="J13" s="6">
+        <v>3</v>
+      </c>
       <c r="K13" s="6">
         <f>(SUM(J13:J13)/5)*0.5</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L13" s="6">
         <f>I13+G13</f>
         <v>4.2249999999999996</v>
       </c>
       <c r="M13" s="6">
-        <f>INT(L13*10)/10+IF(MOD(L13*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.2</v>
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="N13" s="1" t="str">
         <f>IF(L13&lt;3,3-L13,"No aplica")</f>
@@ -3434,18 +3462,20 @@
         <f>H14*0.5</f>
         <v>2</v>
       </c>
-      <c r="J14" s="6"/>
+      <c r="J14" s="6">
+        <v>2</v>
+      </c>
       <c r="K14" s="6">
         <f>(SUM(J14:J14)/5)*0.5</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L14" s="6">
         <f>I14+G14</f>
         <v>4.5</v>
       </c>
       <c r="M14" s="6">
-        <f>INT(L14*10)/10+IF(MOD(L14*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.5</v>
+        <f t="shared" si="0"/>
+        <v>4.7</v>
       </c>
       <c r="N14" s="1" t="str">
         <f>IF(L14&lt;3,3-L14,"No aplica")</f>
@@ -3488,7 +3518,7 @@
         <v>4.8125</v>
       </c>
       <c r="M15" s="6">
-        <f>INT(L15*10)/10+IF(MOD(L15*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="0"/>
         <v>4.8</v>
       </c>
       <c r="N15" s="1" t="str">
@@ -3532,7 +3562,7 @@
         <v>4.3000000000000007</v>
       </c>
       <c r="M16" s="6">
-        <f>INT(L16*10)/10+IF(MOD(L16*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="0"/>
         <v>4.3</v>
       </c>
       <c r="N16" s="1" t="str">
@@ -3560,24 +3590,26 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="H17" s="1">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="I17" s="6">
         <f>H17*0.5</f>
-        <v>1.85</v>
-      </c>
-      <c r="J17" s="6"/>
+        <v>0.85</v>
+      </c>
+      <c r="J17" s="6">
+        <v>2</v>
+      </c>
       <c r="K17" s="6">
         <f>(SUM(J17:J17)/5)*0.5</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L17" s="6">
         <f>I17+G17</f>
-        <v>4.1500000000000004</v>
+        <v>3.15</v>
       </c>
       <c r="M17" s="6">
-        <f>INT(L17*10)/10+IF(MOD(L17*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.1999999999999993</v>
+        <f t="shared" si="0"/>
+        <v>3.4000000000000004</v>
       </c>
       <c r="N17" s="1" t="str">
         <f>IF(L17&lt;3,3-L17,"No aplica")</f>
@@ -3610,18 +3642,20 @@
         <f>H18*0.5</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="J18" s="6"/>
+      <c r="J18" s="6">
+        <v>2</v>
+      </c>
       <c r="K18" s="6">
         <f>(SUM(J18:J18)/5)*0.5</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L18" s="6">
         <f>I18+G18</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="M18" s="6">
-        <f>INT(L18*10)/10+IF(MOD(L18*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>4.8</v>
       </c>
       <c r="N18" s="1" t="str">
         <f>IF(L18&lt;3,3-L18,"No aplica")</f>
@@ -3654,18 +3688,20 @@
         <f>H19*0.5</f>
         <v>2.35</v>
       </c>
-      <c r="J19" s="6"/>
+      <c r="J19" s="6">
+        <v>3</v>
+      </c>
       <c r="K19" s="6">
         <f>(SUM(J19:J19)/5)*0.5</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L19" s="6">
         <f>I19+G19</f>
         <v>4.7750000000000004</v>
       </c>
       <c r="M19" s="6">
-        <f>INT(L19*10)/10+IF(MOD(L19*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>5.0999999999999996</v>
       </c>
       <c r="N19" s="1" t="str">
         <f>IF(L19&lt;3,3-L19,"No aplica")</f>
@@ -3698,18 +3734,20 @@
         <f>H20*0.5</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="J20" s="6"/>
+      <c r="J20" s="6">
+        <v>2</v>
+      </c>
       <c r="K20" s="6">
         <f>(SUM(J20:J20)/5)*0.5</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L20" s="6">
         <f>I20+G20</f>
         <v>4.5750000000000002</v>
       </c>
       <c r="M20" s="6">
-        <f>INT(L20*10)/10+IF(MOD(L20*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>4.8</v>
       </c>
       <c r="N20" s="1" t="str">
         <f>IF(L20&lt;3,3-L20,"No aplica")</f>
@@ -3742,18 +3780,20 @@
         <f>H21*0.5</f>
         <v>2.15</v>
       </c>
-      <c r="J21" s="6"/>
+      <c r="J21" s="6">
+        <v>2</v>
+      </c>
       <c r="K21" s="6">
         <f>(SUM(J21:J21)/5)*0.5</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L21" s="6">
         <f>I21+G21</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="M21" s="6">
-        <f>INT(L21*10)/10+IF(MOD(L21*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>4.8</v>
       </c>
       <c r="N21" s="1" t="str">
         <f>IF(L21&lt;3,3-L21,"No aplica")</f>
@@ -3796,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="6">
-        <f>INT(L22*10)/10+IF(MOD(L22*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N22" s="1">
@@ -3830,18 +3870,20 @@
         <f>H23*0.5</f>
         <v>1.5</v>
       </c>
-      <c r="J23" s="6"/>
+      <c r="J23" s="6">
+        <v>1</v>
+      </c>
       <c r="K23" s="6">
         <f>(SUM(J23:J23)/5)*0.5</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L23" s="6">
         <f>I23+G23</f>
         <v>3.9750000000000001</v>
       </c>
       <c r="M23" s="6">
-        <f>INT(L23*10)/10+IF(MOD(L23*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N23" s="1" t="str">
         <f>IF(L23&lt;3,3-L23,"No aplica")</f>
@@ -3884,7 +3926,7 @@
         <v>3.9499999999999997</v>
       </c>
       <c r="M24" s="6">
-        <f>INT(L24*10)/10+IF(MOD(L24*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="N24" s="1" t="str">
@@ -3928,7 +3970,7 @@
         <v>4.1749999999999998</v>
       </c>
       <c r="M25" s="6">
-        <f>INT(L25*10)/10+IF(MOD(L25*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="0"/>
         <v>4.1999999999999993</v>
       </c>
       <c r="N25" s="1" t="str">
@@ -3972,7 +4014,7 @@
         <v>4.4249999999999998</v>
       </c>
       <c r="M26" s="6">
-        <f>INT(L26*10)/10+IF(MOD(L26*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="0"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="N26" s="1" t="str">
@@ -4006,18 +4048,20 @@
         <f>H27*0.5</f>
         <v>1.85</v>
       </c>
-      <c r="J27" s="6"/>
+      <c r="J27" s="6">
+        <v>2</v>
+      </c>
       <c r="K27" s="6">
         <f>(SUM(J27:J27)/5)*0.5</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L27" s="6">
         <f>I27+G27</f>
         <v>4.1500000000000004</v>
       </c>
       <c r="M27" s="6">
-        <f>INT(L27*10)/10+IF(MOD(L27*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.1999999999999993</v>
+        <f t="shared" si="0"/>
+        <v>4.3999999999999995</v>
       </c>
       <c r="N27" s="1" t="str">
         <f>IF(L27&lt;3,3-L27,"No aplica")</f>
@@ -4050,18 +4094,20 @@
         <f>H28*0.5</f>
         <v>1.65</v>
       </c>
-      <c r="J28" s="6"/>
+      <c r="J28" s="6">
+        <v>1</v>
+      </c>
       <c r="K28" s="6">
         <f>(SUM(J28:J28)/5)*0.5</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L28" s="6">
         <f>I28+G28</f>
         <v>4.0749999999999993</v>
       </c>
       <c r="M28" s="6">
-        <f>INT(L28*10)/10+IF(MOD(L28*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.0999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>4.1999999999999993</v>
       </c>
       <c r="N28" s="1" t="str">
         <f>IF(L28&lt;3,3-L28,"No aplica")</f>
@@ -4094,18 +4140,20 @@
         <f>H29*0.5</f>
         <v>1.85</v>
       </c>
-      <c r="J29" s="6"/>
+      <c r="J29" s="6">
+        <v>3</v>
+      </c>
       <c r="K29" s="6">
         <f>(SUM(J29:J29)/5)*0.5</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L29" s="6">
         <f>I29+G29</f>
         <v>4.3000000000000007</v>
       </c>
       <c r="M29" s="6">
-        <f>INT(L29*10)/10+IF(MOD(L29*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.3</v>
+        <f t="shared" si="0"/>
+        <v>4.5999999999999996</v>
       </c>
       <c r="N29" s="1" t="str">
         <f>IF(L29&lt;3,3-L29,"No aplica")</f>
@@ -4138,18 +4186,20 @@
         <f>H30*0.5</f>
         <v>1.9</v>
       </c>
-      <c r="J30" s="6"/>
+      <c r="J30" s="6">
+        <v>1</v>
+      </c>
       <c r="K30" s="6">
         <f>(SUM(J30:J30)/5)*0.5</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L30" s="6">
         <f>I30+G30</f>
         <v>4.2750000000000004</v>
       </c>
       <c r="M30" s="6">
-        <f>INT(L30*10)/10+IF(MOD(L30*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.3</v>
+        <f t="shared" si="0"/>
+        <v>4.3999999999999995</v>
       </c>
       <c r="N30" s="1" t="str">
         <f>IF(L30&lt;3,3-L30,"No aplica")</f>
@@ -4182,18 +4232,20 @@
         <f>H31*0.5</f>
         <v>1.5</v>
       </c>
-      <c r="J31" s="6"/>
+      <c r="J31" s="6">
+        <v>2</v>
+      </c>
       <c r="K31" s="6">
         <f>(SUM(J31:J31)/5)*0.5</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L31" s="6">
         <f>I31+G31</f>
         <v>3.8</v>
       </c>
       <c r="M31" s="6">
-        <f>INT(L31*10)/10+IF(MOD(L31*10,1)&gt;=0.5,0.1,0)</f>
-        <v>3.8</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="N31" s="1" t="str">
         <f>IF(L31&lt;3,3-L31,"No aplica")</f>
@@ -4220,24 +4272,26 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="H32" s="1">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I32" s="6">
         <f>H32*0.5</f>
-        <v>0.75</v>
-      </c>
-      <c r="J32" s="6"/>
+        <v>0.85</v>
+      </c>
+      <c r="J32" s="6">
+        <v>1</v>
+      </c>
       <c r="K32" s="6">
         <f>(SUM(J32:J32)/5)*0.5</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L32" s="6">
         <f>I32+G32</f>
-        <v>3.2</v>
+        <v>3.3000000000000003</v>
       </c>
       <c r="M32" s="6">
-        <f>INT(L32*10)/10+IF(MOD(L32*10,1)&gt;=0.5,0.1,0)</f>
-        <v>3.2</v>
+        <f t="shared" si="0"/>
+        <v>3.4</v>
       </c>
       <c r="N32" s="1" t="str">
         <f>IF(L32&lt;3,3-L32,"No aplica")</f>
@@ -4245,14 +4299,14 @@
       </c>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="35">
+      <c r="A33" s="36">
         <v>1011098258</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35" t="s">
+      <c r="B33" s="37"/>
+      <c r="C33" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="36"/>
+      <c r="D33" s="21"/>
       <c r="E33" s="1">
         <v>4.4000000000000004</v>
       </c>
@@ -4270,18 +4324,20 @@
         <f>H33*0.5</f>
         <v>1.65</v>
       </c>
-      <c r="J33" s="6"/>
+      <c r="J33" s="6">
+        <v>1</v>
+      </c>
       <c r="K33" s="6">
         <f>(SUM(J33:J33)/5)*0.5</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L33" s="6">
         <f>I33+G33</f>
         <v>3.9499999999999997</v>
       </c>
       <c r="M33" s="6">
-        <f>INT(L33*10)/10+IF(MOD(L33*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N33" s="1" t="str">
         <f>IF(L33&lt;3,3-L33,"No aplica")</f>
@@ -4324,7 +4380,7 @@
         <v>4.5</v>
       </c>
       <c r="M34" s="6">
-        <f>INT(L34*10)/10+IF(MOD(L34*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
       <c r="N34" s="1" t="str">
@@ -4358,18 +4414,20 @@
         <f>H35*0.5</f>
         <v>1.9</v>
       </c>
-      <c r="J35" s="6"/>
+      <c r="J35" s="6">
+        <v>2</v>
+      </c>
       <c r="K35" s="6">
         <f>(SUM(J35:J35)/5)*0.5</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L35" s="6">
         <f>I35+G35</f>
         <v>4.1500000000000004</v>
       </c>
       <c r="M35" s="6">
-        <f>INT(L35*10)/10+IF(MOD(L35*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.1999999999999993</v>
+        <f t="shared" si="0"/>
+        <v>4.3999999999999995</v>
       </c>
       <c r="N35" s="1" t="str">
         <f>IF(L35&lt;3,3-L35,"No aplica")</f>
@@ -4402,18 +4460,20 @@
         <f>H36*0.5</f>
         <v>1.65</v>
       </c>
-      <c r="J36" s="6"/>
+      <c r="J36" s="6">
+        <v>1</v>
+      </c>
       <c r="K36" s="6">
         <f>(SUM(J36:J36)/5)*0.5</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L36" s="6">
         <f>I36+G36</f>
         <v>4.0749999999999993</v>
       </c>
       <c r="M36" s="6">
-        <f>INT(L36*10)/10+IF(MOD(L36*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.0999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>4.1999999999999993</v>
       </c>
       <c r="N36" s="1" t="str">
         <f>IF(L36&lt;3,3-L36,"No aplica")</f>
@@ -4456,7 +4516,7 @@
         <v>4.8125</v>
       </c>
       <c r="M37" s="6">
-        <f>INT(L37*10)/10+IF(MOD(L37*10,1)&gt;=0.5,0.1,0)</f>
+        <f t="shared" si="0"/>
         <v>4.8</v>
       </c>
       <c r="N37" s="1" t="str">
@@ -4490,18 +4550,20 @@
         <f>H38*0.5</f>
         <v>1.5</v>
       </c>
-      <c r="J38" s="6"/>
+      <c r="J38" s="6">
+        <v>1</v>
+      </c>
       <c r="K38" s="6">
         <f>(SUM(J38:J38)/5)*0.5</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L38" s="6">
         <f>I38+G38</f>
         <v>3.9750000000000001</v>
       </c>
       <c r="M38" s="6">
-        <f>INT(L38*10)/10+IF(MOD(L38*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N38" s="1" t="str">
         <f>IF(L38&lt;3,3-L38,"No aplica")</f>
@@ -4509,14 +4571,14 @@
       </c>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="14" t="s">
+      <c r="B39" s="47"/>
+      <c r="C39" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="16"/>
+      <c r="D39" s="27"/>
       <c r="E39" s="1">
         <v>4.9000000000000004</v>
       </c>
@@ -4534,18 +4596,20 @@
         <f>H39*0.5</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="J39" s="6"/>
+      <c r="J39" s="6">
+        <v>1</v>
+      </c>
       <c r="K39" s="6">
         <f>(SUM(J39:J39)/5)*0.5</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L39" s="6">
         <f>I39+G39</f>
         <v>4.4250000000000007</v>
       </c>
       <c r="M39" s="6">
-        <f>INT(L39*10)/10+IF(MOD(L39*10,1)&gt;=0.5,0.1,0)</f>
-        <v>4.4000000000000004</v>
+        <f t="shared" si="0"/>
+        <v>4.5</v>
       </c>
       <c r="N39" s="1" t="str">
         <f>IF(L39&lt;3,3-L39,"No aplica")</f>
@@ -4560,7 +4624,7 @@
       <sortCondition ref="C7"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="A1:B1"/>
@@ -4575,6 +4639,7 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A33:B33"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:F39">
     <cfRule type="expression" dxfId="7" priority="11">
